--- a/carddata/text-of-joker.cardpool.xlsx
+++ b/carddata/text-of-joker.cardpool.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1082734-497A-4505-B08E-CBF7E4DA606F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AC10E0-05FC-44F9-8270-F0BD8D13C1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DC8CCAA9-C70A-4410-9BDB-26BCE8FF7367}"/>
+    <workbookView xWindow="40275" yWindow="2955" windowWidth="21600" windowHeight="11175" xr2:uid="{DC8CCAA9-C70A-4410-9BDB-26BCE8FF7367}"/>
   </bookViews>
   <sheets>
-    <sheet name="ver1_0" sheetId="1" r:id="rId1"/>
+    <sheet name="JOKER" sheetId="2" r:id="rId1"/>
+    <sheet name="ver1_0" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="387">
   <si>
     <t>1-0-001</t>
   </si>
@@ -1096,6 +1097,142 @@
   </si>
   <si>
     <t>evolve</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DEATH</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JUSTICE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE STAR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE MAGICIAN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE CHARIOT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE MOON</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>THE EMPEROR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JOKER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリムゾンブレイク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>no</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>JK-07</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ability</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対戦相手の対戦相手の全てのユニットに５０００ダメージを与える。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたの全てのユニットの行動権を回復する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディバインシールド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">シューティングスター	</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対戦相手のユニットを２体まで選ぶ。それらを手札に戻す。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワンダフルハンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたはカードを５枚引く。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マッシヴサージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あなたの全てのユニットの基本ＢＰ＋５０００する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>明天凶殺</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対戦相手の手札を全て破壊する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディスペアーレイド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対戦相手のユニットを２体までランダムで破壊する。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1503,6 +1640,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A7BBE5-DAC6-4F14-9850-D1A136F62622}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.4140625" customWidth="1"/>
+    <col min="6" max="6" width="63.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96E1FE6C-5652-4627-8BD3-FC4754A31176}">
   <dimension ref="A1:I101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
